--- a/results/Int All Data -0.6/Rando_7_permute.xlsx
+++ b/results/Int All Data -0.6/Rando_7_permute.xlsx
@@ -440,1393 +440,1393 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8943269525316355</v>
+        <v>0.9011396149728568</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8936207378423701</v>
+        <v>0.9036549866888992</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9070388169384153</v>
+        <v>0.9018894499657353</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9059208739535074</v>
+        <v>0.9028451491064351</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9056263875598842</v>
+        <v>0.9049487925268354</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9070388169384153</v>
+        <v>0.9035363631483043</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9070388169384153</v>
+        <v>0.8996521823573438</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9077450316276807</v>
+        <v>0.8941497080400312</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9085834888663615</v>
+        <v>0.8952376497301462</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.908156759923323</v>
+        <v>0.8951640281317403</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.903845850189324</v>
+        <v>0.8969295648549043</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9051110363710433</v>
+        <v>0.8837487328400488</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9047579290264106</v>
+        <v>0.8837787341348415</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9050374147726375</v>
+        <v>0.8718889446807705</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9050374147726375</v>
+        <v>0.8651799051327478</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9024334208107929</v>
+        <v>0.8655330124773806</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9070524359472356</v>
+        <v>0.8691090878658974</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9070524359472356</v>
+        <v>0.8691090878658974</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9190717046735701</v>
+        <v>0.8627353917379592</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9193661910671934</v>
+        <v>0.8651771418555959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9050496521428819</v>
+        <v>0.8710177228701449</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.911655068797706</v>
+        <v>0.8745924166200857</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.909963153672948</v>
+        <v>0.8744601740706704</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9112283398546674</v>
+        <v>0.8784765974110462</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9094628031315035</v>
+        <v>0.8820662918083833</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9100953962223632</v>
+        <v>0.873797579685018</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.90585810808677</v>
+        <v>0.8766960600404859</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9066965653254508</v>
+        <v>0.8752836306619549</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.905490000094741</v>
+        <v>0.8746510375710952</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.889260681250454</v>
+        <v>0.8558041057561432</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.893086241090405</v>
+        <v>0.8554509984115104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8907031119237778</v>
+        <v>0.8540535696803757</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8911298408668165</v>
+        <v>0.8587025861116111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8911298408668165</v>
+        <v>0.8654852472580395</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8979275026606411</v>
+        <v>0.8654852472580395</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8958252408788169</v>
+        <v>0.8583644794143748</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8968109413143094</v>
+        <v>0.858011372069742</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.898487855791671</v>
+        <v>0.8616160671144755</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8998266635717962</v>
+        <v>0.8443138072274698</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.900179770916429</v>
+        <v>0.8363982024487373</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8970004231761581</v>
+        <v>0.8374575244826357</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8950440229525696</v>
+        <v>0.840253763583481</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8794472971991423</v>
+        <v>0.8403273851818868</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8817281851111469</v>
+        <v>0.8403273851818868</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8856123659021073</v>
+        <v>0.8385618484587229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8826688836044503</v>
+        <v>0.8396211704926213</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8864794427970049</v>
+        <v>0.8134612256950037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8949103987645783</v>
+        <v>0.8214504520721421</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8913057037198447</v>
+        <v>0.8155948704101967</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8875687661256959</v>
+        <v>0.7903770057444585</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8991040665965584</v>
+        <v>0.7858602318626383</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8926745127947627</v>
+        <v>0.777032548246819</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8927031324509794</v>
+        <v>0.7884056048734736</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8961183456338642</v>
+        <v>0.8002053904431665</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8928081369827541</v>
+        <v>0.8092389382068068</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8777745276375085</v>
+        <v>0.8107836101347532</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8418556748238608</v>
+        <v>0.8028093844050112</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8294519158195248</v>
+        <v>0.8152267624181675</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8183583449390974</v>
+        <v>0.8159329771074331</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8106213662905453</v>
+        <v>0.8172717848875584</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.825391872175536</v>
+        <v>0.8186842142660893</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8212718259419617</v>
+        <v>0.8034269768484745</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8209187185973289</v>
+        <v>0.8025148980113879</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.807955988100539</v>
+        <v>0.8013819543790837</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.807955988100539</v>
+        <v>0.7882433610292654</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8022176483406126</v>
+        <v>0.7876843895368115</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8008202196094779</v>
+        <v>0.7738682011539446</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7804136152191832</v>
+        <v>0.7821082936210931</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7777359996589326</v>
+        <v>0.7858738508714587</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7551807499060486</v>
+        <v>0.7842691763539269</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7548276425614158</v>
+        <v>0.7794579160784834</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7528562416904309</v>
+        <v>0.7798110234231161</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7508112192210401</v>
+        <v>0.7787367007418216</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7507239786138138</v>
+        <v>0.7773678916669036</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7507239786138138</v>
+        <v>0.7770147843222708</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7582728570390933</v>
+        <v>0.776661676977638</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7835657249418133</v>
+        <v>0.7754851130417207</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7843455612294847</v>
+        <v>0.7682321026486406</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7715914581576679</v>
+        <v>0.7788553242824163</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7577466501185841</v>
+        <v>0.7748975218930501</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7611468626540725</v>
+        <v>0.7865350636185351</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7464772163851282</v>
+        <v>0.7828131266717826</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.729675307039567</v>
+        <v>0.633695441066404</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6873010440450588</v>
+        <v>0.6375060002589585</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6722796720700578</v>
+        <v>0.6109493278130951</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6610238573454222</v>
+        <v>0.6105962204684623</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.642367789030895</v>
+        <v>0.5975312487170499</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.642367789030895</v>
+        <v>0.5922346385475583</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6356287481880797</v>
+        <v>0.5954126046492533</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6357023697864855</v>
+        <v>0.5862318136888013</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.6294650611236906</v>
+        <v>0.5611611922198747</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.580794868515378</v>
+        <v>0.5615142995645075</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.559814291985233</v>
+        <v>0.5583363334628126</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.570850623553227</v>
+        <v>0.5342514124293786</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.578178637183289</v>
+        <v>0.5368704070386195</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5042714343461139</v>
+        <v>0.5379297290725179</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5034329771074331</v>
+        <v>0.5442856612759077</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5068754283079586</v>
+        <v>0.5446387686205405</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5017996829336845</v>
+        <v>0.5446387686205405</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5005631164081819</v>
+        <v>0.5389154295080103</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.4944144299911891</v>
+        <v>0.5401956163371262</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.4947675373358219</v>
+        <v>0.5187883108639425</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.498797579685018</v>
+        <v>0.5170963957391845</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4978855008479313</v>
+        <v>0.5329126046492533</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4974737725522891</v>
+        <v>0.536723163841808</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4872064215402981</v>
+        <v>0.5420933956097053</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4975473941506949</v>
+        <v>0.5420933956097053</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5028426226816105</v>
+        <v>0.5375766217278851</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5021364079923449</v>
+        <v>0.5276896160781676</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.498797579685018</v>
+        <v>0.5184352035193098</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.4999155226699258</v>
+        <v>0.5152572374176149</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.4973265293554774</v>
+        <v>0.5103137345927561</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4956646155255122</v>
+        <v>0.5125796218573644</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.4446223468591802</v>
+        <v>0.5125796218573644</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4677896625012237</v>
+        <v>0.5131385933498183</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4684958771904893</v>
+        <v>0.5081214689265536</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4456366669508895</v>
+        <v>0.5084745762711864</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4571105831935904</v>
+        <v>0.5043845313324049</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5095638995998775</v>
+        <v>0.5046640170786318</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5063123118997768</v>
+        <v>0.5016332941737486</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.505562476906898</v>
+        <v>0.5007062146892656</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.498794816407866</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4981772239644027</v>
+        <v>0.5003531073446328</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4974273889715241</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.497706874717751</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4961322014950119</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4961322014950119</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4961322014950119</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4976618727755619</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4994710298023388</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4976032518245525</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4970442803320986</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4970442803320986</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4967497939384752</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4983967071210442</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4983967071210442</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4978377356285903</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4994410285075461</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1836,7 +1836,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1846,37 +1846,37 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4997205142537731</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,57 +1886,57 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5000736215984058</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5000736215984058</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5003531073446328</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
